--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-28).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-28).xlsx
@@ -935,22 +935,22 @@
     <t>214</t>
   </si>
   <si>
-    <t>20</t>
+    <t>17</t>
   </si>
   <si>
-    <t>R$ 8.816,52</t>
+    <t>R$ 8.759,64</t>
   </si>
   <si>
-    <t>95.3</t>
+    <t>94.8</t>
   </si>
   <si>
     <t>62.9</t>
   </si>
   <si>
-    <t>5.85</t>
+    <t>5.83</t>
   </si>
   <si>
-    <t>19.6</t>
+    <t>19.7</t>
   </si>
   <si>
     <t>7.0</t>
@@ -959,7 +959,7 @@
     <t>6.5</t>
   </si>
   <si>
-    <t>35.2%</t>
+    <t>35.5%</t>
   </si>
   <si>
     <t>15.7%</t>
@@ -6855,7 +6855,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6885,14 +6885,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>6479.8800000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>98</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>5.6024509803921569</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>19.548932051282051</v>
+      </c>
+      <c r="R36" s="8">
+        <v>6.5683756410256411</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.35897435897435898</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9144,7 +9156,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9174,10 +9186,16 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>38.899999999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>1</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
+      <c r="P51" s="7">
+        <v>0.43330000000000002</v>
+      </c>
       <c r="Q51" s="8"/>
       <c r="R51" s="8"/>
       <c r="S51" s="8"/>
@@ -14846,7 +14864,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14874,14 +14892,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>8725.4400000000005</v>
+      </c>
+      <c r="N89" s="6">
+        <v>84</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>8.2928571428571427</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>24.48658536585366</v>
+      </c>
+      <c r="R89" s="8">
+        <v>7.5247975609756104</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.1951219512195122</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
